--- a/data/trans_dic/P56$privada-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P56$privada-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, tiene ayuda privada cuando tiene dificultades en la actividades básicas</t>
+          <t>Población a la que, al menos, tiene ayuda privada cuando tiene dificultades en la actividades básicas (tasa de respuesta: 96,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,94; 17,92</t>
+          <t>2,09; 18,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,4; 18,92</t>
+          <t>3,17; 18,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,49; 19,73</t>
+          <t>3,21; 20,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,44; 22,88</t>
+          <t>10,42; 24,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,76; 17,28</t>
+          <t>4,63; 18,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,94; 19,12</t>
+          <t>8,28; 18,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,01; 22,43</t>
+          <t>8,64; 21,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14,33; 22,29</t>
+          <t>14,6; 22,33</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,21; 15,09</t>
+          <t>5,23; 15,49</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,66; 16,5</t>
+          <t>8,04; 16,62</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8,62; 19,72</t>
+          <t>8,53; 18,98</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,41; 21,27</t>
+          <t>14,22; 20,76</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,75; 66,26</t>
+          <t>14,21; 70,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,95; 26,7</t>
+          <t>5,21; 26,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 68,96</t>
+          <t>0,0; 69,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,17; 56,07</t>
+          <t>8,19; 62,24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,36; 43,26</t>
+          <t>4,19; 45,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,17; 28,1</t>
+          <t>10,98; 28,16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,47</t>
+          <t>0,0; 42,52</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,6; 38,61</t>
+          <t>4,54; 32,5</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,21; 44,09</t>
+          <t>11,07; 43,04</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,0; 23,82</t>
+          <t>11,34; 24,89</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22,85; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,29</t>
+          <t>0,0; 52,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,24</t>
+          <t>0,0; 41,93</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1042,17 +1042,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18,23; 100,0</t>
+          <t>17,84; 100,0</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 72,6</t>
+          <t>0,0; 66,98</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,82; 29,11</t>
+          <t>2,96; 31,82</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,78; 16,46</t>
+          <t>1,77; 16,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,0; 17,28</t>
+          <t>3,93; 18,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,35; 22,84</t>
+          <t>7,05; 22,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,49; 21,58</t>
+          <t>10,23; 21,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,86; 19,65</t>
+          <t>5,63; 19,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,41; 19,85</t>
+          <t>9,71; 19,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,66; 22,64</t>
+          <t>9,59; 22,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,81; 22,2</t>
+          <t>14,68; 21,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,77; 15,98</t>
+          <t>6,11; 16,57</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,13; 17,73</t>
+          <t>9,36; 17,61</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,24; 20,07</t>
+          <t>10,64; 20,96</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,46; 20,07</t>
+          <t>14,76; 20,18</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, tiene ayuda privada cuando tiene dificultades en la actividades básicas</t>
+          <t>Población a la que, al menos, tiene ayuda privada cuando tiene dificultades en la actividades básicas (tasa de respuesta: 96,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>857; 7910</t>
+          <t>922; 7952</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3006; 12938</t>
+          <t>2167; 12672</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2543; 11187</t>
+          <t>1817; 11371</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6410; 15538</t>
+          <t>7073; 16461</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3972; 14411</t>
+          <t>3862; 15136</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14763; 35560</t>
+          <t>15402; 34911</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11430; 32019</t>
+          <t>12336; 30668</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>28749; 44712</t>
+          <t>29274; 44791</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6645; 19251</t>
+          <t>6673; 19760</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>19480; 41954</t>
+          <t>20454; 42279</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17197; 39317</t>
+          <t>17019; 37849</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>38676; 57109</t>
+          <t>38178; 55730</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1268</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 1710</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1538; 7408</t>
+          <t>1589; 7836</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1613; 7238</t>
+          <t>1411; 7160</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4668</t>
+          <t>0; 4710</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>961; 6596</t>
+          <t>964; 7321</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1107; 10982</t>
+          <t>1062; 11523</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4701; 11825</t>
+          <t>4620; 11849</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 4853</t>
+          <t>0; 4641</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>962; 8066</t>
+          <t>948; 6788</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4099; 16121</t>
+          <t>4046; 15736</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7608; 16481</t>
+          <t>7847; 17216</t>
         </is>
       </c>
     </row>
@@ -1925,17 +1925,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>225; 986</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 1877</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3516</t>
+          <t>0; 3395</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 2668</t>
+          <t>0; 2713</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1965,17 +1965,17 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>986; 5409</t>
+          <t>965; 5409</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 5734</t>
+          <t>0; 5290</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>365; 3769</t>
+          <t>384; 4120</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>858; 7949</t>
+          <t>854; 7968</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3142; 13566</t>
+          <t>3089; 14249</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5299; 16468</t>
+          <t>5085; 16395</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10648; 21900</t>
+          <t>10383; 21714</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5480; 18381</t>
+          <t>5267; 18327</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19016; 40115</t>
+          <t>19632; 39764</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16591; 38885</t>
+          <t>16480; 39014</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>36895; 55297</t>
+          <t>36571; 53818</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8182; 22663</t>
+          <t>8667; 23499</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>25624; 49764</t>
+          <t>26278; 49422</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>24973; 48944</t>
+          <t>25946; 51109</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>50685; 70366</t>
+          <t>51759; 70742</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P56$privada-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P56$privada-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,74%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,09; 18,02</t>
+          <t>1,99; 19,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,17; 18,53</t>
+          <t>4,45; 18,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,21; 20,06</t>
+          <t>3,82; 19,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,42; 24,24</t>
+          <t>10,23; 24,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,63; 18,15</t>
+          <t>4,96; 19,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,28; 18,77</t>
+          <t>8,09; 18,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,64; 21,49</t>
+          <t>8,8; 21,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14,6; 22,33</t>
+          <t>14,8; 22,68</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,23; 15,49</t>
+          <t>4,74; 15,52</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8,04; 16,62</t>
+          <t>8,07; 16,87</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8,53; 18,98</t>
+          <t>8,71; 19,25</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,22; 20,76</t>
+          <t>14,47; 21,72</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,28%</t>
         </is>
       </c>
     </row>
@@ -867,12 +867,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,21; 70,09</t>
+          <t>13,18; 66,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,21; 26,42</t>
+          <t>5,49; 25,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -882,37 +882,37 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,19; 62,24</t>
+          <t>8,4; 62,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,19; 45,4</t>
+          <t>4,26; 44,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,98; 28,16</t>
+          <t>10,66; 27,74</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,52</t>
+          <t>0,0; 42,97</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,54; 32,5</t>
+          <t>4,63; 35,41</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,07; 43,04</t>
+          <t>10,7; 42,82</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,34; 24,89</t>
+          <t>10,26; 22,78</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>9,74%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,42</t>
+          <t>0,0; 35,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,93</t>
+          <t>0,0; 41,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1047,12 +1047,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 66,98</t>
+          <t>0,0; 68,47</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,96; 31,82</t>
+          <t>2,6; 25,1</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,12%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,77; 16,5</t>
+          <t>1,84; 16,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,93; 18,15</t>
+          <t>4,05; 18,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,05; 22,74</t>
+          <t>7,12; 22,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,23; 21,4</t>
+          <t>9,51; 20,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,63; 19,59</t>
+          <t>5,61; 20,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,71; 19,67</t>
+          <t>9,53; 20,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,59; 22,71</t>
+          <t>9,47; 23,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,68; 21,6</t>
+          <t>14,62; 21,71</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,11; 16,57</t>
+          <t>5,55; 16,22</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,36; 17,61</t>
+          <t>9,26; 18,02</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,64; 20,96</t>
+          <t>10,5; 20,87</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,76; 20,18</t>
+          <t>14,49; 20,4</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10903</t>
+          <t>11706</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>36363</t>
+          <t>39630</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>47266</t>
+          <t>51336</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>922; 7952</t>
+          <t>878; 8443</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2167; 12672</t>
+          <t>3043; 12852</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1817; 11371</t>
+          <t>2164; 11063</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7073; 16461</t>
+          <t>7388; 17651</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3862; 15136</t>
+          <t>4135; 16210</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15402; 34911</t>
+          <t>15047; 34160</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12336; 30668</t>
+          <t>12565; 30897</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>29274; 44791</t>
+          <t>32136; 49259</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6673; 19760</t>
+          <t>6047; 19801</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>20454; 42279</t>
+          <t>20535; 42903</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17019; 37849</t>
+          <t>17377; 38388</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>38178; 55730</t>
+          <t>41884; 62873</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3678</t>
+          <t>3787</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7923</t>
+          <t>8694</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>11601</t>
+          <t>12481</t>
         </is>
       </c>
     </row>
@@ -1722,12 +1722,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1589; 7836</t>
+          <t>1474; 7386</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1411; 7160</t>
+          <t>1569; 7210</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1737,37 +1737,37 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>964; 7321</t>
+          <t>988; 7389</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1062; 11523</t>
+          <t>1082; 11347</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4620; 11849</t>
+          <t>5122; 13331</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 4641</t>
+          <t>0; 4689</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>948; 6788</t>
+          <t>966; 7397</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4046; 15736</t>
+          <t>3912; 15655</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7847; 17216</t>
+          <t>7864; 17459</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>601</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>873</t>
+          <t>890</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1490</t>
+          <t>1492</t>
         </is>
       </c>
     </row>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3395</t>
+          <t>0; 2561</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 2713</t>
+          <t>0; 3372</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1970,12 +1970,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 5290</t>
+          <t>0; 5408</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>384; 4120</t>
+          <t>399; 3844</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15198</t>
+          <t>16095</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>45158</t>
+          <t>49214</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>60357</t>
+          <t>65309</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>854; 7968</t>
+          <t>887; 7995</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3089; 14249</t>
+          <t>3182; 14551</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5085; 16395</t>
+          <t>5130; 16313</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10383; 21714</t>
+          <t>10269; 22237</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5267; 18327</t>
+          <t>5244; 19030</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19632; 39764</t>
+          <t>19266; 40544</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16480; 39014</t>
+          <t>16272; 40246</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>36571; 53818</t>
+          <t>39980; 59342</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8667; 23499</t>
+          <t>7866; 23003</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>26278; 49422</t>
+          <t>25981; 50572</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>25946; 51109</t>
+          <t>25617; 50892</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>51759; 70742</t>
+          <t>55257; 77801</t>
         </is>
       </c>
     </row>
